--- a/attendance.xlsx
+++ b/attendance.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,6 +445,303 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>30-09-2026</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>CSE 30-09-2026</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>CSE 2026-09-30</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>cSE 30-09-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>26BCE11604</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pranit Seth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>26BAS10104</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pratyaksha Janga</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>26BAI10252</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Swayam Sharma</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>26BAI10779</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>C:\Users\prani\AppData\Local\Programs\Python\Python313\python.exe "c:/Users/prani/OneDrive/Desktop/Python Learning/QR-attendance_system/QR_attendance_system.py"</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>26BCE10900</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Piyush Kumar Thakur</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>26BCE11605</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sarthak Seth</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Absent</t>
         </is>
       </c>
     </row>
